--- a/artfynd/A 54098-2025 artfynd.xlsx
+++ b/artfynd/A 54098-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129728281</v>
       </c>
       <c r="B2" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129728073</v>
       </c>
       <c r="B3" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>129728074</v>
       </c>
       <c r="B4" t="n">
-        <v>79154</v>
+        <v>79155</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129728076</v>
       </c>
       <c r="B5" t="n">
-        <v>79154</v>
+        <v>79155</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         <v>129728071</v>
       </c>
       <c r="B6" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129728078</v>
+        <v>129728075</v>
       </c>
       <c r="B7" t="n">
-        <v>79075</v>
+        <v>79155</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1182,21 +1182,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715189</v>
+        <v>715252</v>
       </c>
       <c r="R7" t="n">
-        <v>7312795</v>
+        <v>7312776</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1250,6 +1250,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1268,10 +1269,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129728075</v>
+        <v>129728078</v>
       </c>
       <c r="B8" t="n">
-        <v>79154</v>
+        <v>79076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1279,21 +1280,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1303,10 +1304,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715252</v>
+        <v>715189</v>
       </c>
       <c r="R8" t="n">
-        <v>7312776</v>
+        <v>7312795</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,12 +1334,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1347,7 +1348,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1369,7 +1369,7 @@
         <v>129728079</v>
       </c>
       <c r="B9" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>129728069</v>
       </c>
       <c r="B10" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>129728082</v>
       </c>
       <c r="B11" t="n">
-        <v>82910</v>
+        <v>82911</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>129728077</v>
       </c>
       <c r="B12" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>129728072</v>
       </c>
       <c r="B13" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>129728080</v>
       </c>
       <c r="B14" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 54098-2025 artfynd.xlsx
+++ b/artfynd/A 54098-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129728281</v>
       </c>
       <c r="B2" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129728073</v>
       </c>
       <c r="B3" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>129728074</v>
       </c>
       <c r="B4" t="n">
-        <v>79155</v>
+        <v>79160</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129728076</v>
       </c>
       <c r="B5" t="n">
-        <v>79155</v>
+        <v>79160</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129728075</v>
+        <v>129728078</v>
       </c>
       <c r="B7" t="n">
-        <v>79155</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1182,21 +1182,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715252</v>
+        <v>715189</v>
       </c>
       <c r="R7" t="n">
-        <v>7312776</v>
+        <v>7312795</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1250,7 +1250,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1269,10 +1268,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129728078</v>
+        <v>129728075</v>
       </c>
       <c r="B8" t="n">
-        <v>79076</v>
+        <v>79160</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1280,21 +1279,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1304,10 +1303,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715189</v>
+        <v>715252</v>
       </c>
       <c r="R8" t="n">
-        <v>7312795</v>
+        <v>7312776</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1334,12 +1333,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1348,6 +1347,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1369,7 +1369,7 @@
         <v>129728079</v>
       </c>
       <c r="B9" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>129728082</v>
       </c>
       <c r="B11" t="n">
-        <v>82911</v>
+        <v>82916</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>129728077</v>
       </c>
       <c r="B12" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>129728080</v>
       </c>
       <c r="B14" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 54098-2025 artfynd.xlsx
+++ b/artfynd/A 54098-2025 artfynd.xlsx
@@ -1171,10 +1171,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129728078</v>
+        <v>129728075</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>79160</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1182,21 +1182,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715189</v>
+        <v>715252</v>
       </c>
       <c r="R7" t="n">
-        <v>7312795</v>
+        <v>7312776</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1250,6 +1250,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1268,10 +1269,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129728075</v>
+        <v>129728078</v>
       </c>
       <c r="B8" t="n">
-        <v>79160</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1279,21 +1280,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1303,10 +1304,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715252</v>
+        <v>715189</v>
       </c>
       <c r="R8" t="n">
-        <v>7312776</v>
+        <v>7312795</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,12 +1334,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1347,7 +1348,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1366,10 +1366,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129728079</v>
+        <v>129728069</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1377,21 +1377,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715419</v>
+        <v>715267</v>
       </c>
       <c r="R9" t="n">
-        <v>7312815</v>
+        <v>7312740</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1431,12 +1431,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>fodersök</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1463,10 +1468,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129728069</v>
+        <v>129728079</v>
       </c>
       <c r="B10" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1474,21 +1479,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1498,10 +1503,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>715267</v>
+        <v>715419</v>
       </c>
       <c r="R10" t="n">
-        <v>7312740</v>
+        <v>7312815</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1528,17 +1533,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>fodersök</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 54098-2025 artfynd.xlsx
+++ b/artfynd/A 54098-2025 artfynd.xlsx
@@ -873,7 +873,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129728074</v>
+        <v>129728076</v>
       </c>
       <c r="B4" t="n">
         <v>79160</v>
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715267</v>
+        <v>715195</v>
       </c>
       <c r="R4" t="n">
-        <v>7312720</v>
+        <v>7312781</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -938,12 +938,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,7 +971,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129728076</v>
+        <v>129728074</v>
       </c>
       <c r="B5" t="n">
         <v>79160</v>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715195</v>
+        <v>715267</v>
       </c>
       <c r="R5" t="n">
-        <v>7312781</v>
+        <v>7312720</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 54098-2025 artfynd.xlsx
+++ b/artfynd/A 54098-2025 artfynd.xlsx
@@ -873,7 +873,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129728076</v>
+        <v>129728074</v>
       </c>
       <c r="B4" t="n">
         <v>79160</v>
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715195</v>
+        <v>715267</v>
       </c>
       <c r="R4" t="n">
-        <v>7312781</v>
+        <v>7312720</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -938,12 +938,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,7 +971,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129728074</v>
+        <v>129728076</v>
       </c>
       <c r="B5" t="n">
         <v>79160</v>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715267</v>
+        <v>715195</v>
       </c>
       <c r="R5" t="n">
-        <v>7312720</v>
+        <v>7312781</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1171,10 +1171,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129728075</v>
+        <v>129728078</v>
       </c>
       <c r="B7" t="n">
-        <v>79160</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1182,21 +1182,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715252</v>
+        <v>715189</v>
       </c>
       <c r="R7" t="n">
-        <v>7312776</v>
+        <v>7312795</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1250,7 +1250,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1269,10 +1268,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129728078</v>
+        <v>129728075</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>79160</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1280,21 +1279,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1304,10 +1303,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715189</v>
+        <v>715252</v>
       </c>
       <c r="R8" t="n">
-        <v>7312795</v>
+        <v>7312776</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1334,12 +1333,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1348,6 +1347,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1366,10 +1366,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129728069</v>
+        <v>129728079</v>
       </c>
       <c r="B9" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1377,21 +1377,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715267</v>
+        <v>715419</v>
       </c>
       <c r="R9" t="n">
-        <v>7312740</v>
+        <v>7312815</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1431,17 +1431,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>fodersök</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1468,10 +1463,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129728079</v>
+        <v>129728069</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1479,21 +1474,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1503,10 +1498,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>715419</v>
+        <v>715267</v>
       </c>
       <c r="R10" t="n">
-        <v>7312815</v>
+        <v>7312740</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1533,12 +1528,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>fodersök</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 54098-2025 artfynd.xlsx
+++ b/artfynd/A 54098-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129728281</v>
       </c>
       <c r="B2" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129728073</v>
       </c>
       <c r="B3" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129728078</v>
+        <v>129728075</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>79160</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1182,21 +1182,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715189</v>
+        <v>715252</v>
       </c>
       <c r="R7" t="n">
-        <v>7312795</v>
+        <v>7312776</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1250,6 +1250,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1268,10 +1269,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129728075</v>
+        <v>129728078</v>
       </c>
       <c r="B8" t="n">
-        <v>79160</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1279,21 +1280,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1303,10 +1304,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715252</v>
+        <v>715189</v>
       </c>
       <c r="R8" t="n">
-        <v>7312776</v>
+        <v>7312795</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,12 +1334,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1347,7 +1348,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>129728077</v>
       </c>
       <c r="B12" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 54098-2025 artfynd.xlsx
+++ b/artfynd/A 54098-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129728281</v>
       </c>
       <c r="B2" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129728073</v>
       </c>
       <c r="B3" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1366,10 +1366,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129728079</v>
+        <v>129728069</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1377,21 +1377,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715419</v>
+        <v>715267</v>
       </c>
       <c r="R9" t="n">
-        <v>7312815</v>
+        <v>7312740</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1431,12 +1431,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>fodersök</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1463,10 +1468,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129728069</v>
+        <v>129728079</v>
       </c>
       <c r="B10" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1474,21 +1479,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1498,10 +1503,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>715267</v>
+        <v>715419</v>
       </c>
       <c r="R10" t="n">
-        <v>7312740</v>
+        <v>7312815</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1528,17 +1533,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>fodersök</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1568,7 +1568,7 @@
         <v>129728082</v>
       </c>
       <c r="B11" t="n">
-        <v>82916</v>
+        <v>82918</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>129728077</v>
       </c>
       <c r="B12" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 54098-2025 artfynd.xlsx
+++ b/artfynd/A 54098-2025 artfynd.xlsx
@@ -1366,10 +1366,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129728069</v>
+        <v>129728079</v>
       </c>
       <c r="B9" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1377,21 +1377,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715267</v>
+        <v>715419</v>
       </c>
       <c r="R9" t="n">
-        <v>7312740</v>
+        <v>7312815</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1431,17 +1431,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>fodersök</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1468,10 +1463,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129728079</v>
+        <v>129728069</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1479,21 +1474,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1503,10 +1498,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>715419</v>
+        <v>715267</v>
       </c>
       <c r="R10" t="n">
-        <v>7312815</v>
+        <v>7312740</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1533,12 +1528,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>fodersök</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 54098-2025 artfynd.xlsx
+++ b/artfynd/A 54098-2025 artfynd.xlsx
@@ -1171,10 +1171,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129728075</v>
+        <v>129728078</v>
       </c>
       <c r="B7" t="n">
-        <v>79160</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1182,21 +1182,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715252</v>
+        <v>715189</v>
       </c>
       <c r="R7" t="n">
-        <v>7312776</v>
+        <v>7312795</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1250,7 +1250,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1269,10 +1268,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129728078</v>
+        <v>129728075</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>79160</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1280,21 +1279,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1304,10 +1303,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715189</v>
+        <v>715252</v>
       </c>
       <c r="R8" t="n">
-        <v>7312795</v>
+        <v>7312776</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1334,12 +1333,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1348,6 +1347,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54098-2025 artfynd.xlsx
+++ b/artfynd/A 54098-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129728281</v>
       </c>
       <c r="B2" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129728073</v>
       </c>
       <c r="B3" t="n">
-        <v>91897</v>
+        <v>91900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,10 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129728074</v>
+        <v>129728076</v>
       </c>
       <c r="B4" t="n">
-        <v>79160</v>
+        <v>79163</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715267</v>
+        <v>715195</v>
       </c>
       <c r="R4" t="n">
-        <v>7312720</v>
+        <v>7312781</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -938,12 +938,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129728076</v>
+        <v>129728074</v>
       </c>
       <c r="B5" t="n">
-        <v>79160</v>
+        <v>79163</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715195</v>
+        <v>715267</v>
       </c>
       <c r="R5" t="n">
-        <v>7312781</v>
+        <v>7312720</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1072,7 +1072,7 @@
         <v>129728071</v>
       </c>
       <c r="B6" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129728078</v>
+        <v>129728075</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>79163</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1182,21 +1182,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715189</v>
+        <v>715252</v>
       </c>
       <c r="R7" t="n">
-        <v>7312795</v>
+        <v>7312776</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1250,6 +1250,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1268,10 +1269,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129728075</v>
+        <v>129728078</v>
       </c>
       <c r="B8" t="n">
-        <v>79160</v>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1279,21 +1280,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1303,10 +1304,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715252</v>
+        <v>715189</v>
       </c>
       <c r="R8" t="n">
-        <v>7312776</v>
+        <v>7312795</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,12 +1334,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1347,7 +1348,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1369,7 +1369,7 @@
         <v>129728079</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>129728069</v>
       </c>
       <c r="B10" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>129728082</v>
       </c>
       <c r="B11" t="n">
-        <v>82918</v>
+        <v>82921</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>129728077</v>
       </c>
       <c r="B12" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>129728072</v>
       </c>
       <c r="B13" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>129728080</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 54098-2025 artfynd.xlsx
+++ b/artfynd/A 54098-2025 artfynd.xlsx
@@ -1171,10 +1171,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129728075</v>
+        <v>129728078</v>
       </c>
       <c r="B7" t="n">
-        <v>79163</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1182,21 +1182,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715252</v>
+        <v>715189</v>
       </c>
       <c r="R7" t="n">
-        <v>7312776</v>
+        <v>7312795</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1250,7 +1250,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1269,10 +1268,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129728078</v>
+        <v>129728075</v>
       </c>
       <c r="B8" t="n">
-        <v>79084</v>
+        <v>79163</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1280,21 +1279,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1304,10 +1303,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715189</v>
+        <v>715252</v>
       </c>
       <c r="R8" t="n">
-        <v>7312795</v>
+        <v>7312776</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1334,12 +1333,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1348,6 +1347,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54098-2025 artfynd.xlsx
+++ b/artfynd/A 54098-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129728281</v>
       </c>
       <c r="B2" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129728073</v>
       </c>
       <c r="B3" t="n">
-        <v>91900</v>
+        <v>91903</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,10 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129728076</v>
+        <v>129728074</v>
       </c>
       <c r="B4" t="n">
-        <v>79163</v>
+        <v>79166</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715195</v>
+        <v>715267</v>
       </c>
       <c r="R4" t="n">
-        <v>7312781</v>
+        <v>7312720</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -938,12 +938,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129728074</v>
+        <v>129728076</v>
       </c>
       <c r="B5" t="n">
-        <v>79163</v>
+        <v>79166</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715267</v>
+        <v>715195</v>
       </c>
       <c r="R5" t="n">
-        <v>7312720</v>
+        <v>7312781</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1072,7 +1072,7 @@
         <v>129728071</v>
       </c>
       <c r="B6" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129728078</v>
+        <v>129728075</v>
       </c>
       <c r="B7" t="n">
-        <v>79084</v>
+        <v>79166</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1182,21 +1182,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715189</v>
+        <v>715252</v>
       </c>
       <c r="R7" t="n">
-        <v>7312795</v>
+        <v>7312776</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1250,6 +1250,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1268,10 +1269,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129728075</v>
+        <v>129728078</v>
       </c>
       <c r="B8" t="n">
-        <v>79163</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1279,21 +1280,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1303,10 +1304,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715252</v>
+        <v>715189</v>
       </c>
       <c r="R8" t="n">
-        <v>7312776</v>
+        <v>7312795</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,12 +1334,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1347,7 +1348,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1369,7 +1369,7 @@
         <v>129728079</v>
       </c>
       <c r="B9" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>129728069</v>
       </c>
       <c r="B10" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>129728082</v>
       </c>
       <c r="B11" t="n">
-        <v>82921</v>
+        <v>82924</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>129728077</v>
       </c>
       <c r="B12" t="n">
-        <v>91622</v>
+        <v>91625</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>129728072</v>
       </c>
       <c r="B13" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>129728080</v>
       </c>
       <c r="B14" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 54098-2025 artfynd.xlsx
+++ b/artfynd/A 54098-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129728281</v>
       </c>
       <c r="B2" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129728073</v>
       </c>
       <c r="B3" t="n">
-        <v>91903</v>
+        <v>91904</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>129728074</v>
       </c>
       <c r="B4" t="n">
-        <v>79166</v>
+        <v>79167</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129728076</v>
       </c>
       <c r="B5" t="n">
-        <v>79166</v>
+        <v>79167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>129728075</v>
       </c>
       <c r="B7" t="n">
-        <v>79166</v>
+        <v>79167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>129728078</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>129728079</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>129728082</v>
       </c>
       <c r="B11" t="n">
-        <v>82924</v>
+        <v>82925</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>129728077</v>
       </c>
       <c r="B12" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>129728080</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 54098-2025 artfynd.xlsx
+++ b/artfynd/A 54098-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129728281</v>
       </c>
       <c r="B2" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129728073</v>
       </c>
       <c r="B3" t="n">
-        <v>91904</v>
+        <v>91921</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>129728074</v>
       </c>
       <c r="B4" t="n">
-        <v>79167</v>
+        <v>79168</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129728076</v>
       </c>
       <c r="B5" t="n">
-        <v>79167</v>
+        <v>79168</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129728075</v>
+        <v>129728078</v>
       </c>
       <c r="B7" t="n">
-        <v>79167</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1182,21 +1182,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715252</v>
+        <v>715189</v>
       </c>
       <c r="R7" t="n">
-        <v>7312776</v>
+        <v>7312795</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1250,7 +1250,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1269,10 +1268,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129728078</v>
+        <v>129728075</v>
       </c>
       <c r="B8" t="n">
-        <v>79088</v>
+        <v>79168</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1280,21 +1279,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1304,10 +1303,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715189</v>
+        <v>715252</v>
       </c>
       <c r="R8" t="n">
-        <v>7312795</v>
+        <v>7312776</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1334,12 +1333,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1348,6 +1347,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1369,7 +1369,7 @@
         <v>129728079</v>
       </c>
       <c r="B9" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>129728082</v>
       </c>
       <c r="B11" t="n">
-        <v>82925</v>
+        <v>82931</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>129728077</v>
       </c>
       <c r="B12" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>129728080</v>
       </c>
       <c r="B14" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 54098-2025 artfynd.xlsx
+++ b/artfynd/A 54098-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129728281</v>
+        <v>129728073</v>
       </c>
       <c r="B2" t="n">
-        <v>91628</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tjartsebäcken, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>715364</v>
+        <v>715369</v>
       </c>
       <c r="R2" t="n">
-        <v>7312749</v>
+        <v>7312802</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -757,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -776,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129728073</v>
+        <v>129728074</v>
       </c>
       <c r="B3" t="n">
-        <v>91926</v>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>715369</v>
+        <v>715267</v>
       </c>
       <c r="R3" t="n">
-        <v>7312802</v>
+        <v>7312720</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -841,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -855,6 +851,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -873,10 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129728076</v>
+        <v>129728075</v>
       </c>
       <c r="B4" t="n">
-        <v>79168</v>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715195</v>
+        <v>715252</v>
       </c>
       <c r="R4" t="n">
-        <v>7312781</v>
+        <v>7312776</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -938,12 +935,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +968,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129728074</v>
+        <v>129728076</v>
       </c>
       <c r="B5" t="n">
-        <v>79168</v>
+        <v>79406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,10 +1003,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715267</v>
+        <v>715195</v>
       </c>
       <c r="R5" t="n">
-        <v>7312720</v>
+        <v>7312781</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1036,12 +1033,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1069,10 +1066,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129728071</v>
+        <v>129728281</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1080,34 +1077,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjartsebäcken, Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>715211</v>
+        <v>715364</v>
       </c>
       <c r="R6" t="n">
-        <v>7312692</v>
+        <v>7312749</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1134,17 +1134,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>fodersök</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1153,6 +1148,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1171,10 +1167,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129728078</v>
+        <v>129728082</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1182,21 +1178,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1206,10 +1202,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715189</v>
+        <v>715237</v>
       </c>
       <c r="R7" t="n">
-        <v>7312795</v>
+        <v>7312791</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,12 +1232,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1250,6 +1246,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1268,10 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129728075</v>
+        <v>79750155</v>
       </c>
       <c r="B8" t="n">
-        <v>79168</v>
+        <v>93189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1279,37 +1276,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tjartsebäcken, Pi lm</t>
+          <t>Ljusträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715252</v>
+        <v>715654</v>
       </c>
       <c r="R8" t="n">
-        <v>7312776</v>
+        <v>7312795</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1333,12 +1330,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2018-09-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2018-09-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1347,67 +1349,66 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129728079</v>
+        <v>79749201</v>
       </c>
       <c r="B9" t="n">
-        <v>79089</v>
+        <v>90691</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6276</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tjartsebäcken, Pi lm</t>
+          <t>Ljusträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715419</v>
+        <v>715652</v>
       </c>
       <c r="R9" t="n">
-        <v>7312815</v>
+        <v>7312798</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1431,12 +1432,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2018-09-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2018-09-19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1451,44 +1457,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129728069</v>
+        <v>129728078</v>
       </c>
       <c r="B10" t="n">
-        <v>57737</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1498,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>715267</v>
+        <v>715189</v>
       </c>
       <c r="R10" t="n">
-        <v>7312740</v>
+        <v>7312795</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1528,17 +1534,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>fodersök</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1565,32 +1566,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129728082</v>
+        <v>129728079</v>
       </c>
       <c r="B11" t="n">
-        <v>82931</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1600,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>715237</v>
+        <v>715419</v>
       </c>
       <c r="R11" t="n">
-        <v>7312791</v>
+        <v>7312815</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1630,12 +1631,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1644,7 +1645,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1663,30 +1663,34 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129728077</v>
+        <v>129728080</v>
       </c>
       <c r="B12" t="n">
-        <v>91648</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1694,10 +1698,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>715444</v>
+        <v>715395</v>
       </c>
       <c r="R12" t="n">
-        <v>7312791</v>
+        <v>7312759</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1756,14 +1760,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129728072</v>
+        <v>129728069</v>
       </c>
       <c r="B13" t="n">
-        <v>57737</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1791,10 +1795,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>715237</v>
+        <v>715267</v>
       </c>
       <c r="R13" t="n">
-        <v>7312750</v>
+        <v>7312740</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1821,12 +1825,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -1858,32 +1862,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129728080</v>
+        <v>129728071</v>
       </c>
       <c r="B14" t="n">
-        <v>79089</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1893,10 +1897,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>715395</v>
+        <v>715211</v>
       </c>
       <c r="R14" t="n">
-        <v>7312759</v>
+        <v>7312692</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1931,6 +1935,11 @@
           <t>2025-11-07</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>fodersök</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -1952,6 +1961,108 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129728072</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tjartsebäcken, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>715237</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7312750</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>fodersök</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54098-2025 artfynd.xlsx
+++ b/artfynd/A 54098-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1760,27 +1760,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129728069</v>
+        <v>134665329</v>
       </c>
       <c r="B13" t="n">
-        <v>57950</v>
+        <v>57896</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1791,17 +1791,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tjartsebäcken, Pi lm</t>
+          <t>Ljusträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>715267</v>
+        <v>715226</v>
       </c>
       <c r="R13" t="n">
-        <v>7312740</v>
+        <v>7312782</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1825,17 +1825,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>fodersök</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1850,19 +1850,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129728071</v>
+        <v>129728069</v>
       </c>
       <c r="B14" t="n">
         <v>57950</v>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>715211</v>
+        <v>715267</v>
       </c>
       <c r="R14" t="n">
-        <v>7312692</v>
+        <v>7312740</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1927,12 +1927,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -1964,7 +1964,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129728072</v>
+        <v>129728071</v>
       </c>
       <c r="B15" t="n">
         <v>57950</v>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>715237</v>
+        <v>715211</v>
       </c>
       <c r="R15" t="n">
-        <v>7312750</v>
+        <v>7312692</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2063,6 +2063,108 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129728072</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Tjartsebäcken, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>715237</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7312750</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>fodersök</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54098-2025 artfynd.xlsx
+++ b/artfynd/A 54098-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129728073</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129728074</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -965,6 +980,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129728075</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1063,6 +1083,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129728076</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1164,6 +1189,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129728281</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1262,6 +1292,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129728082</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1364,6 +1399,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79750155</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1466,6 +1506,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79749201</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1563,6 +1608,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129728078</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1660,6 +1710,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129728079</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1757,6 +1812,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129728080</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1859,6 +1919,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665329</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1961,6 +2026,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129728069</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2063,6 +2133,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129728071</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2165,8 +2240,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129728072</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>